--- a/output/pdf_financials_xlsx/NTX.xlsx
+++ b/output/pdf_financials_xlsx/NTX.xlsx
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.165404</v>
+        <v>1.248568</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.176376</v>
+        <v>2.249012</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.434088</v>
+        <v>3.228571</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.308919</v>
+        <v>1.609953</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.165404</v>
+        <v>-1.248568</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.176376</v>
+        <v>-2.249012</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.434088</v>
+        <v>-3.228571</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.308919</v>
+        <v>-1.609953</v>
       </c>
     </row>
     <row r="12">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">

--- a/output/pdf_financials_xlsx/NTX.xlsx
+++ b/output/pdf_financials_xlsx/NTX.xlsx
@@ -492,10 +492,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -538,10 +536,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -650,10 +646,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.248568</v>
@@ -3497,7 +3491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8485,6 +8479,182 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.06948799999999999</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>-0.06948799999999999</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Net loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding- basic and diluted</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>4.283684</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
